--- a/Result/profitability/8284.xlsx
+++ b/Result/profitability/8284.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM53"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15375</v>
+        <v>1.22375</v>
       </c>
       <c r="N2" t="n">
-        <v>23.355</v>
+        <v>23.81125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>-0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>0.87125</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>22.9825</v>
+        <v>23.4875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>2.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9225</v>
+        <v>0.97375</v>
       </c>
       <c r="N4" t="n">
-        <v>22.5875</v>
+        <v>22.935</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6862499999999999</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>21.62</v>
+        <v>22.69375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.79</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6187500000000001</v>
+        <v>0.6412500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>21.645</v>
+        <v>22.2175</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>0.51</v>
       </c>
       <c r="N7" t="n">
-        <v>22.11625</v>
+        <v>22.54125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -7159,6 +7159,133 @@
       </c>
       <c r="AM53" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>8284</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>823</v>
+      </c>
+      <c r="D54" t="n">
+        <v>595</v>
+      </c>
+      <c r="E54" t="n">
+        <v>227</v>
+      </c>
+      <c r="F54" t="n">
+        <v>27.61</v>
+      </c>
+      <c r="G54" t="n">
+        <v>106</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>12.91%</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>108</v>
+      </c>
+      <c r="K54" t="n">
+        <v>86</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.35125</v>
+      </c>
+      <c r="N54" t="n">
+        <v>23.8025</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.453125</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>3.419999999999998</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.1413807358412567</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-8.440000000000001</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.4516298633017877</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
